--- a/dataAnalitics/dividend_table.xlsx
+++ b/dataAnalitics/dividend_table.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dividendos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dividendos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -507,10 +507,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.44</v>
+        <v>12.67</v>
       </c>
       <c r="D2" t="n">
-        <v>15.73</v>
+        <v>13.64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="H2" t="n">
-        <v>22.02</v>
+        <v>22.12</v>
       </c>
       <c r="I2" t="n">
-        <v>520</v>
+        <v>106.1</v>
       </c>
       <c r="J2" t="n">
-        <v>669.9400000000001</v>
+        <v>688.6799999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>33.05</v>
+        <v>7.78</v>
       </c>
       <c r="L2" t="n">
-        <v>9.91</v>
+        <v>11.44</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>8.12–10.60</t>
+          <t>8.12–12.17</t>
         </is>
       </c>
     </row>
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="D3" t="n">
-        <v>9.609999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -570,30 +570,30 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>155.56</t>
+          <t>120.39</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.03</v>
+        <v>0.83</v>
       </c>
       <c r="H3" t="n">
-        <v>30.08</v>
+        <v>29.98</v>
       </c>
       <c r="I3" t="n">
-        <v>143.4</v>
+        <v>140.5</v>
       </c>
       <c r="J3" t="n">
-        <v>51.28</v>
+        <v>50.87</v>
       </c>
       <c r="K3" t="n">
-        <v>14.92</v>
+        <v>16.43</v>
       </c>
       <c r="L3" t="n">
-        <v>11.34</v>
+        <v>12.16</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>10.66–16.32</t>
+          <t>10.66–15.67</t>
         </is>
       </c>
     </row>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="D4" t="n">
-        <v>19.9</v>
+        <v>17.64</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -621,30 +621,30 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.82</t>
+          <t>-12.26</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H4" t="n">
-        <v>24.37</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>25.62</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1642.1</v>
+      </c>
       <c r="J4" t="n">
-        <v>778.16</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>781.24</v>
+      </c>
+      <c r="K4" t="n">
+        <v>93.11</v>
       </c>
       <c r="L4" t="n">
-        <v>15.68</v>
+        <v>17.69</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>13.97–20.36</t>
+          <t>13.97–19.21</t>
         </is>
       </c>
     </row>
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="D5" t="n">
-        <v>13.09</v>
+        <v>11.86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -672,30 +672,30 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.99</v>
+        <v>0.78</v>
       </c>
       <c r="H5" t="n">
-        <v>25.13</v>
+        <v>24.55</v>
       </c>
       <c r="I5" t="n">
-        <v>155.4</v>
+        <v>152</v>
       </c>
       <c r="J5" t="n">
-        <v>101.59</v>
+        <v>108.23</v>
       </c>
       <c r="K5" t="n">
-        <v>11.88</v>
+        <v>12.81</v>
       </c>
       <c r="L5" t="n">
-        <v>19.48</v>
+        <v>23.19</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>17.99–25.85</t>
+          <t>17.99–23.81</t>
         </is>
       </c>
     </row>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.69</v>
+        <v>2.81</v>
       </c>
       <c r="D6" t="n">
-        <v>15.8</v>
+        <v>15.42</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -723,30 +723,30 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H6" t="n">
-        <v>19.14</v>
+        <v>19.73</v>
       </c>
       <c r="I6" t="n">
-        <v>244</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>534.17</v>
+        <v>564.92</v>
       </c>
       <c r="K6" t="n">
-        <v>15.45</v>
+        <v>5.7</v>
       </c>
       <c r="L6" t="n">
-        <v>12.98</v>
+        <v>14.07</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>11.13–14.42</t>
+          <t>11.13–14.74</t>
         </is>
       </c>
     </row>
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="D7" t="n">
-        <v>12.56</v>
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -774,26 +774,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>20.74</v>
+        <v>22.08</v>
       </c>
       <c r="I7" t="n">
-        <v>138.5</v>
+        <v>128</v>
       </c>
       <c r="J7" t="n">
-        <v>885.78</v>
+        <v>870.86</v>
       </c>
       <c r="K7" t="n">
-        <v>11.03</v>
+        <v>9.85</v>
       </c>
       <c r="L7" t="n">
-        <v>13.45</v>
+        <v>13</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>11.56</v>
+        <v>11.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>0.78</v>
       </c>
       <c r="H8" t="n">
-        <v>19.16</v>
+        <v>19.5</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
@@ -839,14 +839,14 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>33.2</v>
+        <v>32.35</v>
       </c>
       <c r="L8" t="n">
-        <v>56.47</v>
+        <v>58.05</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>45.88–58.51</t>
+          <t>45.88–59.96</t>
         </is>
       </c>
     </row>
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="D9" t="n">
-        <v>6.64</v>
+        <v>6.61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -874,30 +874,30 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H9" t="n">
-        <v>18.96</v>
+        <v>17.11</v>
       </c>
       <c r="I9" t="n">
-        <v>126</v>
+        <v>343.1</v>
       </c>
       <c r="J9" t="n">
-        <v>66.65000000000001</v>
+        <v>90.62</v>
       </c>
       <c r="K9" t="n">
-        <v>18.97</v>
+        <v>51.93</v>
       </c>
       <c r="L9" t="n">
-        <v>34.33</v>
+        <v>37.39</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>32.83–39.44</t>
+          <t>32.83–37.84</t>
         </is>
       </c>
     </row>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>15.66</v>
+        <v>13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -925,30 +925,30 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.96</v>
+        <v>0.74</v>
       </c>
       <c r="H10" t="n">
-        <v>21.01</v>
+        <v>22.43</v>
       </c>
       <c r="I10" t="n">
-        <v>163.3</v>
+        <v>171.7</v>
       </c>
       <c r="J10" t="n">
-        <v>127.94</v>
+        <v>165.35</v>
       </c>
       <c r="K10" t="n">
-        <v>10.43</v>
+        <v>13.21</v>
       </c>
       <c r="L10" t="n">
-        <v>8.550000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>8.55–11.89</t>
+          <t>8.43–11.42</t>
         </is>
       </c>
     </row>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="D11" t="n">
-        <v>22.91</v>
+        <v>22.16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -976,18 +976,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H11" t="n">
-        <v>31.06</v>
+        <v>31.03</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>45.22</v>
+        <v>41.5</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -995,11 +995,11 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.59–5.34</t>
+          <t>2.45–4.45</t>
         </is>
       </c>
     </row>
